--- a/deliverables/Project-Completion-Checklist.xlsx
+++ b/deliverables/Project-Completion-Checklist.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,16 +29,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="14"/>
+      <color rgb="00002C5F"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -47,7 +85,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="00002C5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F7FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,35 +124,94 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00BFCDDA"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00BFCDDA"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00BFCDDA"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00BFCDDA"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00595959"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00EDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -448,20 +570,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00002C5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
@@ -469,7 +592,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Checklist Item</t>
+          <t>Checklist item</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -484,648 +607,670 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Evidence / Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>Evidence / notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="29" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Requirements</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Confirm VpcCidr is acceptable and does not collide with any other environment or client network.</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Confirm VpcCidr (172.200.0.0/24) with the client — non-RFC1918 range</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Client / HMSG</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3" ht="29" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Requirements</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Confirm ClientVpnCidr does not overlap VPC or on-prem ranges.</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Confirm ClientVpnCidr 10.200.0.0/22 has no overlap</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="29" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Requirements</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Receive CustomerGatewayIp and OnPremCidr from the client.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Receive CustomerGatewayIp + OnPremCidr (for the optional S2S VPN)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="29" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Requirements</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Receive Entra ID Federation Metadata XML from the client.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Receive Entra ID Federation Metadata XML</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="29" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Approve AWS Architecture Design Document (Week 1 deliverable).</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>HMSG / Client</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Architecture design document approved (Week 1)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Client / HMSG</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="29" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Network</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Deploy VPC, subnets, route tables, IGW, and NAT gateway.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Deploy VPC / subnets / route tables / IGW / NAT</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="29" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Network</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Verify VPC flow logs are writing to S3 and lifecycle is in place.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Verify flow logs → S3 and lifecycle rules</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="29" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Verify security groups only allow RDP and MSSQL from Client VPN / on-prem ranges.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Security groups allow RDP / MSSQL only from VPN + on-prem ranges</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="29" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Confirm secret for sysadm exists in Secrets Manager.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>sysadm secret exists in Secrets Manager (NoEcho)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="29" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Launch the Windows Server 2022 EC2 instance in the DB subnet.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>EC2 launched in db-ec1a (m7i.2xlarge · Win 2022)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="29" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Confirm D: 4 TB volume is formatted and available.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>D: 4 TB volume formatted NTFS and mounted</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="29" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Confirm sysadm local account exists and can log in.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>sysadm local account created and tested</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="29" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>VPN</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Import / issue the ACM certificate for Client VPN.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>ACM server certificate issued / imported</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="29" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>VPN</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Create / update IAM SAML provider from the client metadata XML.</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>IAM SAML provider updated with real metadata XML</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="29" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>VPN</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Validate Client VPN endpoint and download client configuration.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Client VPN endpoint validated; .ovpn distributed to ≤10 users</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="29" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>VPN</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Confirm dev access to the DB host over Client VPN.</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>HMSG / Client</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Developer access to the DB host over Client VPN verified</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Client / HMSG</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="29" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>VPN</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>If required, create the Site-to-Site VPN after the client supplies gateway IP and on-prem CIDR.</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>HMSG / Client</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Site-to-Site VPN created and tunnels UP (if required)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Client / HMSG</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="29" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>VPN</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Verify on-prem route propagation to pri/db route tables.</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>On-prem route propagated into pri/db route tables verified</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="29" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Deliver the AWS Infrastructure Resource Inventory (Excel).</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Deliver the Administration Guide.</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Resource inventory delivered</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="29" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Administration guide delivered</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="29" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Deliver Backup / MSSQL EC2 Recovery / VPN Configuration documentation.</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Deliver the Project Completion Checklist.</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Backup / recovery / VPN configuration delivered</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="29" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Completion checklist closed out</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="29" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Handover</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Remove temporary implementation IAM permissions after project completion.</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>HMSG</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Temporary implementation IAM access removed</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>HMSG</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="29" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Handover</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Transfer VPN user management to HMGRS / client ops.</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>VPN user management transferred to HMGRS</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Client / HMGRS</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="29" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Handover</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Obtain final sign-off.</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Final sign-off obtained</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Client / HMSG</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E26"/>
+  <conditionalFormatting sqref="D2:D26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$D2="Done"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$D2="In progress"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>$D2="Blocked"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>$D2="Not started"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Choose: Not started, In progress, Blocked or Done." type="list">
+      <formula1>"Not started,In progress,Blocked,Done"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009AA7B4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Status Legend</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Status legend</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Not yet done</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Work underway</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Completed and verified</t>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Owner: HMSG = implementation team · Client = Hyundai / HMGRS</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/deliverables/Project-Completion-Checklist.xlsx
+++ b/deliverables/Project-Completion-Checklist.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$E$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -752,12 +752,12 @@
     <row r="8" ht="29" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Verify flow logs → S3 and lifecycle rules</t>
+          <t>Security groups allow RDP / MSSQL only from VPN + on-prem ranges</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Security groups allow RDP / MSSQL only from VPN + on-prem ranges</t>
+          <t>sysadm secret exists in Secrets Manager (NoEcho)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -798,12 +798,12 @@
     <row r="10" ht="29" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Compute</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>sysadm secret exists in Secrets Manager (NoEcho)</t>
+          <t>EC2 launched in db-ec1a (m7i.2xlarge · Win 2022)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>EC2 launched in db-ec1a (m7i.2xlarge · Win 2022)</t>
+          <t>D: 4 TB volume formatted NTFS and mounted</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>D: 4 TB volume formatted NTFS and mounted</t>
+          <t>sysadm local account created and tested</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="13" ht="29" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Compute</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>sysadm local account created and tested</t>
+          <t>ACM server certificate issued / imported</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ACM server certificate issued / imported</t>
+          <t>IAM SAML provider updated with real metadata XML</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>IAM SAML provider updated with real metadata XML</t>
+          <t>Client VPN endpoint validated; .ovpn distributed to ≤10 users</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Client VPN endpoint validated; .ovpn distributed to ≤10 users</t>
+          <t>Developer access to the DB host over Client VPN verified</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>HMSG</t>
+          <t>Client / HMSG</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Developer access to the DB host over Client VPN verified</t>
+          <t>Site-to-Site VPN created and tunnels UP (if required)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -987,12 +987,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Site-to-Site VPN created and tunnels UP (if required)</t>
+          <t>On-prem route propagated into pri/db route tables verified</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Client / HMSG</t>
+          <t>HMSG</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1005,12 +1005,12 @@
     <row r="19" ht="29" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>On-prem route propagated into pri/db route tables verified</t>
+          <t>Resource inventory delivered</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Resource inventory delivered</t>
+          <t>Administration guide delivered</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Administration guide delivered</t>
+          <t>Backup / recovery / VPN configuration delivered</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Backup / recovery / VPN configuration delivered</t>
+          <t>Completion checklist closed out</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1097,12 +1097,12 @@
     <row r="23" ht="29" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Handover</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Completion checklist closed out</t>
+          <t>Temporary implementation IAM access removed</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Temporary implementation IAM access removed</t>
+          <t>VPN user management transferred to HMGRS</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>HMSG</t>
+          <t>Client / HMGRS</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>VPN user management transferred to HMGRS</t>
+          <t>Final sign-off obtained</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Client / HMGRS</t>
+          <t>Client / HMSG</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1163,32 +1163,9 @@
       </c>
       <c r="E25" s="5" t="inlineStr"/>
     </row>
-    <row r="26" ht="29" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Handover</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Final sign-off obtained</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Client / HMSG</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E26"/>
-  <conditionalFormatting sqref="D2:D26">
+  <autoFilter ref="A1:E25"/>
+  <conditionalFormatting sqref="D2:D25">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="Done"</formula>
     </cfRule>
@@ -1203,7 +1180,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Choose: Not started, In progress, Blocked or Done." type="list">
+    <dataValidation sqref="D2:D25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Choose: Not started, In progress, Blocked or Done." type="list">
       <formula1>"Not started,In progress,Blocked,Done"</formula1>
     </dataValidation>
   </dataValidations>
